--- a/data/historial/2026-07-25.xlsx
+++ b/data/historial/2026-07-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F762A7C4-DE31-4BB4-A459-D7BBBF50B412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8804928-A003-498A-8DEC-B0146FDD23A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="C2" s="131"/>
       <c r="D2" s="131">
-        <v>0.15894531249999999</v>
+        <v>0.15883608217592593</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="C3" s="131"/>
       <c r="D3" s="131">
-        <v>0.26660440779320982</v>
+        <v>0.2679417920524691</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="C4" s="131"/>
       <c r="D4" s="131">
-        <v>0.2419609375</v>
+        <v>0.24192173032407407</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="C5" s="131"/>
       <c r="D5" s="131">
-        <v>0.24094540895061728</v>
+        <v>0.24213218557098765</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="C6" s="131"/>
       <c r="D6" s="131">
-        <v>0.20030603780864198</v>
+        <v>0.20280762924382717</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="C7" s="131"/>
       <c r="D7" s="131">
-        <v>0.23877879050925929</v>
+        <v>0.24111935763888892</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -27919,7 +27919,7 @@
       </c>
       <c r="C8" s="131"/>
       <c r="D8" s="131">
-        <v>0.23200506365740742</v>
+        <v>0.23348958333333336</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="C9" s="131"/>
       <c r="D9" s="131">
-        <v>0.22446686921296299</v>
+        <v>0.22365986689814815</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -27958,7 +27958,7 @@
       </c>
       <c r="C11" s="131"/>
       <c r="D11" s="131">
-        <v>0.24150000000000002</v>
+        <v>0.24333709490740743</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -27971,7 +27971,7 @@
       </c>
       <c r="C12" s="131"/>
       <c r="D12" s="131">
-        <v>0.27755782214506175</v>
+        <v>0.27909355709876543</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="C13" s="131"/>
       <c r="D13" s="131">
-        <v>0.23645891203703698</v>
+        <v>0.23853395061728389</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -27997,7 +27997,7 @@
       </c>
       <c r="C14" s="131"/>
       <c r="D14" s="131">
-        <v>0.26579002700617282</v>
+        <v>0.2660741705246914</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -28010,7 +28010,7 @@
       </c>
       <c r="C15" s="131"/>
       <c r="D15" s="131">
-        <v>0.2264433834876543</v>
+        <v>0.22851369598765431</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -28023,7 +28023,7 @@
       </c>
       <c r="C16" s="131"/>
       <c r="D16" s="131">
-        <v>0.22483666087962961</v>
+        <v>0.2265993923611111</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -28036,7 +28036,7 @@
       </c>
       <c r="C17" s="131"/>
       <c r="D17" s="131">
-        <v>0.24415104166666668</v>
+        <v>0.24408680555555556</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -28049,7 +28049,7 @@
       </c>
       <c r="C18" s="131"/>
       <c r="D18" s="131">
-        <v>0.24397738233024691</v>
+        <v>0.24430406057098766</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -28062,7 +28062,7 @@
       </c>
       <c r="C19" s="131"/>
       <c r="D19" s="131">
-        <v>0.23725766782407409</v>
+        <v>0.23758434606481482</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -28075,7 +28075,7 @@
       </c>
       <c r="C20" s="131"/>
       <c r="D20" s="131">
-        <v>0.28041565393518519</v>
+        <v>0.28225101273148145</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -28088,7 +28088,7 @@
       </c>
       <c r="C21" s="131"/>
       <c r="D21" s="131">
-        <v>0.2298334297839506</v>
+        <v>0.23041300154320987</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -28101,7 +28101,7 @@
       </c>
       <c r="C22" s="131"/>
       <c r="D22" s="131">
-        <v>0.22383579282407406</v>
+        <v>0.22367274305555554</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="C23" s="131"/>
       <c r="D23" s="131">
-        <v>0.1950274884259259</v>
+        <v>0.19223668981481479</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -28127,7 +28127,7 @@
       </c>
       <c r="C24" s="131"/>
       <c r="D24" s="131">
-        <v>0.24920900848765432</v>
+        <v>0.25047072723765434</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C25" s="131"/>
       <c r="D25" s="131">
-        <v>0.1950795717592593</v>
+        <v>0.19563932291666669</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -28153,7 +28153,7 @@
       </c>
       <c r="C26" s="131"/>
       <c r="D26" s="131">
-        <v>0.2263500675154321</v>
+        <v>0.22714072145061728</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="C27" s="131"/>
       <c r="D27" s="131">
-        <v>0.23228313078703702</v>
+        <v>0.23007523148148146</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -28179,7 +28179,7 @@
       </c>
       <c r="C28" s="131"/>
       <c r="D28" s="131">
-        <v>0.24824594907407405</v>
+        <v>0.24842939814814813</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -28192,7 +28192,7 @@
       </c>
       <c r="C29" s="131"/>
       <c r="D29" s="131">
-        <v>0.21109375</v>
+        <v>0.20947554976851851</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -28205,7 +28205,7 @@
       </c>
       <c r="C30" s="131"/>
       <c r="D30" s="131">
-        <v>0.19017756558641974</v>
+        <v>0.19086766975308642</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="C31" s="131"/>
       <c r="D31" s="131">
-        <v>0.18812813464506173</v>
+        <v>0.18967139274691358</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C32" s="131"/>
       <c r="D32" s="131">
-        <v>0.16095548804012344</v>
+        <v>0.15387456597222221</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -28244,7 +28244,7 @@
       </c>
       <c r="C33" s="131"/>
       <c r="D33" s="131">
-        <v>0.1868296199845679</v>
+        <v>0.18825872878086419</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -28270,7 +28270,7 @@
       </c>
       <c r="C35" s="131"/>
       <c r="D35" s="131">
-        <v>0.12294777199074075</v>
+        <v>0.12331712962962964</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="C36" s="131"/>
       <c r="D36" s="131">
-        <v>0.16340277777777776</v>
+        <v>0.16427115483539093</v>
       </c>
     </row>
   </sheetData>

--- a/data/historial/2026-07-25.xlsx
+++ b/data/historial/2026-07-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8804928-A003-498A-8DEC-B0146FDD23A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFE3F7A-E37D-4AB0-B40B-FB99EF14CFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2054,7 +2054,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2300,6 +2300,9 @@
     <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="18" fillId="34" borderId="25" xfId="47" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2326,10 +2329,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="138">
@@ -2816,1224 +2815,1224 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="152" t="s">
+      <c r="B1" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="152" t="s">
+      <c r="C1" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="152" t="s">
+      <c r="D1" s="142" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="152" t="s">
+      <c r="E1" s="142" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="152" t="s">
+      <c r="F1" s="142" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="152" t="s">
+      <c r="G1" s="142" t="s">
         <v>151</v>
       </c>
-      <c r="H1" s="152" t="s">
+      <c r="H1" s="142" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
+      <c r="A2" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="151">
-        <v>0</v>
-      </c>
-      <c r="C2" s="151">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>81369.085700560303</v>
       </c>
-      <c r="D2" s="151">
+      <c r="D2">
         <v>392477.69350549381</v>
       </c>
-      <c r="E2" s="151">
+      <c r="E2">
         <v>1456802575.9204144</v>
       </c>
-      <c r="F2" s="151">
-        <v>0</v>
-      </c>
-      <c r="G2" s="151">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>658148.040491199</v>
       </c>
-      <c r="H2" s="151">
+      <c r="H2">
         <v>658147.92000000004</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="151" t="s">
+      <c r="A3" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="151">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="151">
+      <c r="C3">
         <v>921.1319812058</v>
       </c>
-      <c r="D3" s="151">
+      <c r="D3">
         <v>1599.8098675634999</v>
       </c>
-      <c r="E3" s="151">
+      <c r="E3">
         <v>21938268.016373243</v>
       </c>
-      <c r="F3" s="151">
-        <v>0</v>
-      </c>
-      <c r="G3" s="151">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>658148.040491199</v>
       </c>
-      <c r="H3" s="151">
+      <c r="H3">
         <v>658147.92000000004</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="151" t="s">
+      <c r="A4" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="151">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="151">
+      <c r="C4">
         <v>548.35611772289997</v>
       </c>
-      <c r="D4" s="151">
+      <c r="D4">
         <v>1432.1880357110001</v>
       </c>
-      <c r="E4" s="151">
+      <c r="E4">
         <v>13945934.946131114</v>
       </c>
-      <c r="F4" s="151">
-        <v>0</v>
-      </c>
-      <c r="G4" s="151">
-        <v>0</v>
-      </c>
-      <c r="H4" s="151">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="151" t="s">
+      <c r="A5" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="151">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="151">
+      <c r="C5">
         <v>1093.0867460280999</v>
       </c>
-      <c r="D5" s="151">
+      <c r="D5">
         <v>4701.2886190585996</v>
       </c>
-      <c r="E5" s="151">
+      <c r="E5">
         <v>24137576.900611538</v>
       </c>
-      <c r="F5" s="151">
-        <v>0</v>
-      </c>
-      <c r="G5" s="151">
-        <v>0</v>
-      </c>
-      <c r="H5" s="151">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="151" t="s">
+      <c r="A6" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="151">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="151">
+      <c r="C6">
         <v>1389.2040674589</v>
       </c>
-      <c r="D6" s="151">
+      <c r="D6">
         <v>3928.9837381102002</v>
       </c>
-      <c r="E6" s="151">
+      <c r="E6">
         <v>33858693.342466839</v>
       </c>
-      <c r="F6" s="151">
-        <v>0</v>
-      </c>
-      <c r="G6" s="151">
-        <v>0</v>
-      </c>
-      <c r="H6" s="151">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="151" t="s">
+      <c r="A7" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="151">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="151">
+      <c r="C7">
         <v>1885.7419025536001</v>
       </c>
-      <c r="D7" s="151">
+      <c r="D7">
         <v>6934.0749171244997</v>
       </c>
-      <c r="E7" s="151">
+      <c r="E7">
         <v>35559935.88760341</v>
       </c>
-      <c r="F7" s="151">
-        <v>0</v>
-      </c>
-      <c r="G7" s="151">
-        <v>0</v>
-      </c>
-      <c r="H7" s="151">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="151" t="s">
+      <c r="A8" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="151">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="151">
+      <c r="C8">
         <v>4317.7249999999003</v>
       </c>
-      <c r="D8" s="151">
+      <c r="D8">
         <v>12166.03</v>
       </c>
-      <c r="E8" s="151">
+      <c r="E8">
         <v>78964296.522824496</v>
       </c>
-      <c r="F8" s="151">
-        <v>0</v>
-      </c>
-      <c r="G8" s="151">
-        <v>0</v>
-      </c>
-      <c r="H8" s="151">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="151" t="s">
+      <c r="A9" t="s">
         <v>271</v>
       </c>
-      <c r="B9" s="151">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="151">
+      <c r="C9">
         <v>880.84876984059997</v>
       </c>
-      <c r="D9" s="151">
+      <c r="D9">
         <v>3094.3865000176002</v>
       </c>
-      <c r="E9" s="151">
+      <c r="E9">
         <v>17745499.922953639</v>
       </c>
-      <c r="F9" s="151">
-        <v>0</v>
-      </c>
-      <c r="G9" s="151">
-        <v>0</v>
-      </c>
-      <c r="H9" s="151">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="151" t="s">
+      <c r="A10" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="151">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="151">
+      <c r="C10">
         <v>468.20654365029998</v>
       </c>
-      <c r="D10" s="151">
+      <c r="D10">
         <v>1855.2826071699001</v>
       </c>
-      <c r="E10" s="151">
+      <c r="E10">
         <v>14401052.837159272</v>
       </c>
-      <c r="F10" s="151">
-        <v>0</v>
-      </c>
-      <c r="G10" s="151">
-        <v>0</v>
-      </c>
-      <c r="H10" s="151">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="151" t="s">
+      <c r="A11" t="s">
         <v>210</v>
       </c>
-      <c r="B11" s="151">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="151">
+      <c r="C11">
         <v>785.01496031730005</v>
       </c>
-      <c r="D11" s="151">
+      <c r="D11">
         <v>2518.4462500157001</v>
       </c>
-      <c r="E11" s="151">
+      <c r="E11">
         <v>14453628.378361048</v>
       </c>
-      <c r="F11" s="151">
-        <v>0</v>
-      </c>
-      <c r="G11" s="151">
-        <v>0</v>
-      </c>
-      <c r="H11" s="151">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="151" t="s">
+      <c r="A12" t="s">
         <v>209</v>
       </c>
-      <c r="B12" s="151">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="151">
+      <c r="C12">
         <v>1373.1402380925999</v>
       </c>
-      <c r="D12" s="151">
+      <c r="D12">
         <v>5088.4467500236997</v>
       </c>
-      <c r="E12" s="151">
+      <c r="E12">
         <v>24141553.199037012</v>
       </c>
-      <c r="F12" s="151">
-        <v>0</v>
-      </c>
-      <c r="G12" s="151">
-        <v>0</v>
-      </c>
-      <c r="H12" s="151">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="151" t="s">
+      <c r="A13" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="151">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="151">
+      <c r="C13">
         <v>1601.6527103144001</v>
       </c>
-      <c r="D13" s="151">
+      <c r="D13">
         <v>3719.3483095387001</v>
       </c>
-      <c r="E13" s="151">
+      <c r="E13">
         <v>31676817.089343239</v>
       </c>
-      <c r="F13" s="151">
-        <v>0</v>
-      </c>
-      <c r="G13" s="151">
-        <v>0</v>
-      </c>
-      <c r="H13" s="151">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="151" t="s">
+      <c r="A14" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="151">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="151">
+      <c r="C14">
         <v>6598.3796527765999</v>
       </c>
-      <c r="D14" s="151">
+      <c r="D14">
         <v>32111.143909222501</v>
       </c>
-      <c r="E14" s="151">
+      <c r="E14">
         <v>102087212.84340489</v>
       </c>
-      <c r="F14" s="151">
-        <v>0</v>
-      </c>
-      <c r="G14" s="151">
-        <v>0</v>
-      </c>
-      <c r="H14" s="151">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="151" t="s">
+      <c r="A15" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="151">
+      <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" s="151">
+      <c r="C15">
         <v>1254.0944444429999</v>
       </c>
-      <c r="D15" s="151">
+      <c r="D15">
         <v>4286.7371785763999</v>
       </c>
-      <c r="E15" s="151">
+      <c r="E15">
         <v>26520702.51038542</v>
       </c>
-      <c r="F15" s="151">
-        <v>0</v>
-      </c>
-      <c r="G15" s="151">
-        <v>0</v>
-      </c>
-      <c r="H15" s="151">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="151" t="s">
+      <c r="A16" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="151">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="151">
+      <c r="C16">
         <v>824.46890872949996</v>
       </c>
-      <c r="D16" s="151">
+      <c r="D16">
         <v>3263.2434524044002</v>
       </c>
-      <c r="E16" s="151">
+      <c r="E16">
         <v>21358590.673529468</v>
       </c>
-      <c r="F16" s="151">
-        <v>0</v>
-      </c>
-      <c r="G16" s="151">
-        <v>0</v>
-      </c>
-      <c r="H16" s="151">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="151" t="s">
+      <c r="A17" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="151">
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="151">
+      <c r="C17">
         <v>1769.1159126969001</v>
       </c>
-      <c r="D17" s="151">
+      <c r="D17">
         <v>5708.1780833392004</v>
       </c>
-      <c r="E17" s="151">
+      <c r="E17">
         <v>39460498.513925046</v>
       </c>
-      <c r="F17" s="151">
-        <v>0</v>
-      </c>
-      <c r="G17" s="151">
-        <v>0</v>
-      </c>
-      <c r="H17" s="151">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="151" t="s">
+      <c r="A18" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="151">
+      <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="151">
+      <c r="C18">
         <v>1995.1146626967</v>
       </c>
-      <c r="D18" s="151">
+      <c r="D18">
         <v>8956.5872619296006</v>
       </c>
-      <c r="E18" s="151">
+      <c r="E18">
         <v>42285720.719740458</v>
       </c>
-      <c r="F18" s="151">
-        <v>0</v>
-      </c>
-      <c r="G18" s="151">
-        <v>0</v>
-      </c>
-      <c r="H18" s="151">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="151" t="s">
+      <c r="A19" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="151">
+      <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="151">
+      <c r="C19">
         <v>1642.3334920601001</v>
       </c>
-      <c r="D19" s="151">
+      <c r="D19">
         <v>6382.0658333417996</v>
       </c>
-      <c r="E19" s="151">
+      <c r="E19">
         <v>35026761.331216544</v>
       </c>
-      <c r="F19" s="151">
-        <v>0</v>
-      </c>
-      <c r="G19" s="151">
-        <v>0</v>
-      </c>
-      <c r="H19" s="151">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="151" t="s">
+      <c r="A20" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="151">
+      <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="151">
+      <c r="C20">
         <v>5374.7170138881002</v>
       </c>
-      <c r="D20" s="151">
+      <c r="D20">
         <v>30575.647921122301</v>
       </c>
-      <c r="E20" s="151">
+      <c r="E20">
         <v>100110391.15793201</v>
       </c>
-      <c r="F20" s="151">
-        <v>0</v>
-      </c>
-      <c r="G20" s="151">
-        <v>0</v>
-      </c>
-      <c r="H20" s="151">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="151" t="s">
+      <c r="A21" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="151">
+      <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="151">
+      <c r="C21">
         <v>646.1340872984</v>
       </c>
-      <c r="D21" s="151">
+      <c r="D21">
         <v>2384.5228690756999</v>
       </c>
-      <c r="E21" s="151">
+      <c r="E21">
         <v>15727434.484158095</v>
       </c>
-      <c r="F21" s="151">
-        <v>0</v>
-      </c>
-      <c r="G21" s="151">
-        <v>0</v>
-      </c>
-      <c r="H21" s="151">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="151" t="s">
+      <c r="A22" t="s">
         <v>276</v>
       </c>
-      <c r="B22" s="151">
+      <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" s="151">
+      <c r="C22">
         <v>445.12689153389999</v>
       </c>
-      <c r="D22" s="151">
+      <c r="D22">
         <v>1796.4244166870001</v>
       </c>
-      <c r="E22" s="151">
+      <c r="E22">
         <v>9560526.8965929467</v>
       </c>
-      <c r="F22" s="151">
-        <v>0</v>
-      </c>
-      <c r="G22" s="151">
-        <v>0</v>
-      </c>
-      <c r="H22" s="151">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="151" t="s">
+      <c r="A23" t="s">
         <v>267</v>
       </c>
-      <c r="B23" s="151">
+      <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" s="151">
+      <c r="C23">
         <v>4613.4269444431002</v>
       </c>
-      <c r="D23" s="151">
+      <c r="D23">
         <v>25032.299678570202</v>
       </c>
-      <c r="E23" s="151">
+      <c r="E23">
         <v>81530925.666284323</v>
       </c>
-      <c r="F23" s="151">
-        <v>0</v>
-      </c>
-      <c r="G23" s="151">
-        <v>0</v>
-      </c>
-      <c r="H23" s="151">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="151" t="s">
+      <c r="A24" t="s">
         <v>266</v>
       </c>
-      <c r="B24" s="151">
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" s="151">
+      <c r="C24">
         <v>3104.2488095231001</v>
       </c>
-      <c r="D24" s="151">
+      <c r="D24">
         <v>28021.333214282</v>
       </c>
-      <c r="E24" s="151">
+      <c r="E24">
         <v>55057645.412610985</v>
       </c>
-      <c r="F24" s="151">
-        <v>0</v>
-      </c>
-      <c r="G24" s="151">
-        <v>0</v>
-      </c>
-      <c r="H24" s="151">
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="151" t="s">
+      <c r="A25" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="151">
+      <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" s="151">
+      <c r="C25">
         <v>934.69273015689998</v>
       </c>
-      <c r="D25" s="151">
+      <c r="D25">
         <v>4311.0360952482997</v>
       </c>
-      <c r="E25" s="151">
+      <c r="E25">
         <v>22052328.865927253</v>
       </c>
-      <c r="F25" s="151">
-        <v>0</v>
-      </c>
-      <c r="G25" s="151">
-        <v>0</v>
-      </c>
-      <c r="H25" s="151">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="151" t="s">
+      <c r="A26" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="151">
+      <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26" s="151">
+      <c r="C26">
         <v>866.07775793179997</v>
       </c>
-      <c r="D26" s="151">
+      <c r="D26">
         <v>2490.1015475970999</v>
       </c>
-      <c r="E26" s="151">
+      <c r="E26">
         <v>14944602.342241667</v>
       </c>
-      <c r="F26" s="151">
-        <v>0</v>
-      </c>
-      <c r="G26" s="151">
-        <v>0</v>
-      </c>
-      <c r="H26" s="151">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="151" t="s">
+      <c r="A27" t="s">
         <v>217</v>
       </c>
-      <c r="B27" s="151">
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" s="151">
+      <c r="C27">
         <v>8358.2722222224002</v>
       </c>
-      <c r="D27" s="151">
+      <c r="D27">
         <v>27737.4</v>
       </c>
-      <c r="E27" s="151">
+      <c r="E27">
         <v>101026373.12925294</v>
       </c>
-      <c r="F27" s="151">
-        <v>0</v>
-      </c>
-      <c r="G27" s="151">
-        <v>0</v>
-      </c>
-      <c r="H27" s="151">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="151" t="s">
+      <c r="A28" t="s">
         <v>219</v>
       </c>
-      <c r="B28" s="151">
+      <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="151">
+      <c r="C28">
         <v>1299.7407142801001</v>
       </c>
-      <c r="D28" s="151">
+      <c r="D28">
         <v>5098.5304642818001</v>
       </c>
-      <c r="E28" s="151">
+      <c r="E28">
         <v>26040173.304788072</v>
       </c>
-      <c r="F28" s="151">
-        <v>0</v>
-      </c>
-      <c r="G28" s="151">
-        <v>0</v>
-      </c>
-      <c r="H28" s="151">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="151" t="s">
+      <c r="A29" t="s">
         <v>211</v>
       </c>
-      <c r="B29" s="151">
+      <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29" s="151">
+      <c r="C29">
         <v>3626.2382936496001</v>
       </c>
-      <c r="D29" s="151">
+      <c r="D29">
         <v>16679.3793333346</v>
       </c>
-      <c r="E29" s="151">
+      <c r="E29">
         <v>60329801.152089536</v>
       </c>
-      <c r="F29" s="151">
-        <v>0</v>
-      </c>
-      <c r="G29" s="151">
-        <v>0</v>
-      </c>
-      <c r="H29" s="151">
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="151" t="s">
+      <c r="A30" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="151">
+      <c r="B30">
         <v>1</v>
       </c>
-      <c r="C30" s="151">
+      <c r="C30">
         <v>468.93190475979998</v>
       </c>
-      <c r="D30" s="151">
+      <c r="D30">
         <v>1516.1996785664001</v>
       </c>
-      <c r="E30" s="151">
+      <c r="E30">
         <v>10133345.955324732</v>
       </c>
-      <c r="F30" s="151">
-        <v>0</v>
-      </c>
-      <c r="G30" s="151">
-        <v>0</v>
-      </c>
-      <c r="H30" s="151">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="151" t="s">
+      <c r="A31" t="s">
         <v>213</v>
       </c>
-      <c r="B31" s="151">
+      <c r="B31">
         <v>1</v>
       </c>
-      <c r="C31" s="151">
+      <c r="C31">
         <v>813.12876984000002</v>
       </c>
-      <c r="D31" s="151">
+      <c r="D31">
         <v>2265.7170833448999</v>
       </c>
-      <c r="E31" s="151">
+      <c r="E31">
         <v>12226089.901296066</v>
       </c>
-      <c r="F31" s="151">
-        <v>0</v>
-      </c>
-      <c r="G31" s="151">
-        <v>0</v>
-      </c>
-      <c r="H31" s="151">
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="151" t="s">
+      <c r="A32" t="s">
         <v>274</v>
       </c>
-      <c r="B32" s="151">
+      <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32" s="151">
+      <c r="C32">
         <v>172.96474206190001</v>
       </c>
-      <c r="D32" s="151">
+      <c r="D32">
         <v>774.7679166611</v>
       </c>
-      <c r="E32" s="151">
+      <c r="E32">
         <v>5914861.5217189686</v>
       </c>
-      <c r="F32" s="151">
-        <v>0</v>
-      </c>
-      <c r="G32" s="151">
-        <v>0</v>
-      </c>
-      <c r="H32" s="151">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="151" t="s">
+      <c r="A33" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="151">
+      <c r="B33">
         <v>1</v>
       </c>
-      <c r="C33" s="151">
+      <c r="C33">
         <v>1254.8154563476</v>
       </c>
-      <c r="D33" s="151">
+      <c r="D33">
         <v>5154.8165833394996</v>
       </c>
-      <c r="E33" s="151">
+      <c r="E33">
         <v>19847876.635364786</v>
       </c>
-      <c r="F33" s="151">
-        <v>0</v>
-      </c>
-      <c r="G33" s="151">
-        <v>0</v>
-      </c>
-      <c r="H33" s="151">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="151" t="s">
+      <c r="A34" t="s">
         <v>270</v>
       </c>
-      <c r="B34" s="151">
+      <c r="B34">
         <v>1</v>
       </c>
-      <c r="C34" s="151">
+      <c r="C34">
         <v>163.21921335210001</v>
       </c>
-      <c r="D34" s="151">
+      <c r="D34">
         <v>1932.7814166661001</v>
       </c>
-      <c r="E34" s="151">
+      <c r="E34">
         <v>5241126.1151039721</v>
       </c>
-      <c r="F34" s="151">
-        <v>0</v>
-      </c>
-      <c r="G34" s="151">
-        <v>0</v>
-      </c>
-      <c r="H34" s="151">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="151" t="s">
+      <c r="A35" t="s">
         <v>268</v>
       </c>
-      <c r="B35" s="151">
+      <c r="B35">
         <v>1</v>
       </c>
-      <c r="C35" s="151">
+      <c r="C35">
         <v>2436.3847222221998</v>
       </c>
-      <c r="D35" s="151">
+      <c r="D35">
         <v>18574.5399999982</v>
       </c>
-      <c r="E35" s="151">
+      <c r="E35">
         <v>35321218.174947955</v>
       </c>
-      <c r="F35" s="151">
-        <v>0</v>
-      </c>
-      <c r="G35" s="151">
-        <v>0</v>
-      </c>
-      <c r="H35" s="151">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="151" t="s">
+      <c r="A36" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="151">
+      <c r="B36">
         <v>1</v>
       </c>
-      <c r="C36" s="151">
+      <c r="C36">
         <v>967.93998015730006</v>
       </c>
-      <c r="D36" s="151">
+      <c r="D36">
         <v>4191.3346607472004</v>
       </c>
-      <c r="E36" s="151">
+      <c r="E36">
         <v>22894552.211635783</v>
       </c>
-      <c r="F36" s="151">
-        <v>0</v>
-      </c>
-      <c r="G36" s="151">
-        <v>0</v>
-      </c>
-      <c r="H36" s="151">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="151" t="s">
+      <c r="A37" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="151">
+      <c r="B37">
         <v>1</v>
       </c>
-      <c r="C37" s="151">
+      <c r="C37">
         <v>922.34910714299997</v>
       </c>
-      <c r="D37" s="151">
+      <c r="D37">
         <v>5556.3775000114001</v>
       </c>
-      <c r="E37" s="151">
+      <c r="E37">
         <v>19388227.995180633</v>
       </c>
-      <c r="F37" s="151">
-        <v>0</v>
-      </c>
-      <c r="G37" s="151">
-        <v>0</v>
-      </c>
-      <c r="H37" s="151">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="151" t="s">
+      <c r="A38" t="s">
         <v>272</v>
       </c>
-      <c r="B38" s="151">
+      <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38" s="151">
+      <c r="C38">
         <v>1485.5</v>
       </c>
-      <c r="D38" s="151">
+      <c r="D38">
         <v>15032.479999997</v>
       </c>
-      <c r="E38" s="151">
+      <c r="E38">
         <v>34613285.663450733</v>
       </c>
-      <c r="F38" s="151">
-        <v>0</v>
-      </c>
-      <c r="G38" s="151">
-        <v>0</v>
-      </c>
-      <c r="H38" s="151">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="151" t="s">
+      <c r="A39" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="151">
+      <c r="B39">
         <v>1</v>
       </c>
-      <c r="C39" s="151">
+      <c r="C39">
         <v>1393.3771103895999</v>
       </c>
-      <c r="D39" s="151">
+      <c r="D39">
         <v>16701.505000001402</v>
       </c>
-      <c r="E39" s="151">
+      <c r="E39">
         <v>32905785.229168605</v>
       </c>
-      <c r="F39" s="151">
-        <v>0</v>
-      </c>
-      <c r="G39" s="151">
-        <v>0</v>
-      </c>
-      <c r="H39" s="151">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="151" t="s">
+      <c r="A40" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="151">
+      <c r="B40">
         <v>1</v>
       </c>
-      <c r="C40" s="151">
+      <c r="C40">
         <v>2361.0676227407998</v>
       </c>
-      <c r="D40" s="151">
+      <c r="D40">
         <v>12569.717519369</v>
       </c>
-      <c r="E40" s="151">
+      <c r="E40">
         <v>37653118.237861037</v>
       </c>
-      <c r="F40" s="151">
-        <v>0</v>
-      </c>
-      <c r="G40" s="151">
-        <v>0</v>
-      </c>
-      <c r="H40" s="151">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="151" t="s">
+      <c r="A41" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="151">
+      <c r="B41">
         <v>1</v>
       </c>
-      <c r="C41" s="151">
+      <c r="C41">
         <v>5239.0556547626002</v>
       </c>
-      <c r="D41" s="151">
+      <c r="D41">
         <v>32322.769416663901</v>
       </c>
-      <c r="E41" s="151">
+      <c r="E41">
         <v>59139346.928738102</v>
       </c>
-      <c r="F41" s="151">
-        <v>0</v>
-      </c>
-      <c r="G41" s="151">
-        <v>0</v>
-      </c>
-      <c r="H41" s="151">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="151" t="s">
+      <c r="A42" t="s">
         <v>214</v>
       </c>
-      <c r="B42" s="151">
+      <c r="B42">
         <v>1</v>
       </c>
-      <c r="C42" s="151">
+      <c r="C42">
         <v>707.19444444440001</v>
       </c>
-      <c r="D42" s="151">
+      <c r="D42">
         <v>6412.8199999994004</v>
       </c>
-      <c r="E42" s="151">
+      <c r="E42">
         <v>14367535.716373395</v>
       </c>
-      <c r="F42" s="151">
-        <v>0</v>
-      </c>
-      <c r="G42" s="151">
-        <v>0</v>
-      </c>
-      <c r="H42" s="151">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="151" t="s">
+      <c r="A43" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="151">
+      <c r="B43">
         <v>1</v>
       </c>
-      <c r="C43" s="151">
+      <c r="C43">
         <v>602.84578372960004</v>
       </c>
-      <c r="D43" s="151">
+      <c r="D43">
         <v>2400.2402889882001</v>
       </c>
-      <c r="E43" s="151">
+      <c r="E43">
         <v>24669197.621924087</v>
       </c>
-      <c r="F43" s="151">
-        <v>0</v>
-      </c>
-      <c r="G43" s="151">
-        <v>0</v>
-      </c>
-      <c r="H43" s="151">
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="151" t="s">
+      <c r="A44" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="151">
+      <c r="B44">
         <v>1</v>
       </c>
-      <c r="C44" s="151">
+      <c r="C44">
         <v>752.22956349260005</v>
       </c>
-      <c r="D44" s="151">
+      <c r="D44">
         <v>4275.4610952479998</v>
       </c>
-      <c r="E44" s="151">
+      <c r="E44">
         <v>14499068.612910941</v>
       </c>
-      <c r="F44" s="151">
-        <v>0</v>
-      </c>
-      <c r="G44" s="151">
-        <v>0</v>
-      </c>
-      <c r="H44" s="151">
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="151" t="s">
+      <c r="A45" t="s">
         <v>275</v>
       </c>
-      <c r="B45" s="151">
+      <c r="B45">
         <v>1</v>
       </c>
-      <c r="C45" s="151">
+      <c r="C45">
         <v>402.446428572</v>
       </c>
-      <c r="D45" s="151">
+      <c r="D45">
         <v>479.95833333079997</v>
       </c>
-      <c r="E45" s="151">
+      <c r="E45">
         <v>7202966.5073920414</v>
       </c>
-      <c r="F45" s="151">
-        <v>0</v>
-      </c>
-      <c r="G45" s="151">
-        <v>0</v>
-      </c>
-      <c r="H45" s="151">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="151" t="s">
+      <c r="A46" t="s">
         <v>154</v>
       </c>
-      <c r="B46" s="151">
+      <c r="B46">
         <v>1</v>
       </c>
-      <c r="C46" s="151">
+      <c r="C46">
         <v>1183.0953670626</v>
       </c>
-      <c r="D46" s="151">
+      <c r="D46">
         <v>2770.6359568347998</v>
       </c>
-      <c r="E46" s="151">
+      <c r="E46">
         <v>14195910.591248116</v>
       </c>
-      <c r="F46" s="151">
-        <v>0</v>
-      </c>
-      <c r="G46" s="151">
-        <v>0</v>
-      </c>
-      <c r="H46" s="151">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="151" t="s">
+      <c r="A47" t="s">
         <v>218</v>
       </c>
-      <c r="B47" s="151">
+      <c r="B47">
         <v>1</v>
       </c>
-      <c r="C47" s="151">
+      <c r="C47">
         <v>1426.2482539676</v>
       </c>
-      <c r="D47" s="151">
+      <c r="D47">
         <v>7672.6542023802003</v>
       </c>
-      <c r="E47" s="151">
+      <c r="E47">
         <v>22646116.253830038</v>
       </c>
-      <c r="F47" s="151">
-        <v>0</v>
-      </c>
-      <c r="G47" s="151">
-        <v>0</v>
-      </c>
-      <c r="H47" s="151">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -9368,7 +9367,7 @@
       <c r="L2" s="103">
         <v>907871.92636018235</v>
       </c>
-      <c r="N2" s="149" t="s">
+      <c r="N2" s="150" t="s">
         <v>37</v>
       </c>
       <c r="O2">
@@ -9431,7 +9430,7 @@
       <c r="L3" s="105">
         <v>707919.37019508681</v>
       </c>
-      <c r="N3" s="149"/>
+      <c r="N3" s="150"/>
       <c r="O3">
         <v>49</v>
       </c>
@@ -9492,7 +9491,7 @@
       <c r="L4" s="105">
         <v>276942.08389738784</v>
       </c>
-      <c r="N4" s="149"/>
+      <c r="N4" s="150"/>
       <c r="O4">
         <v>20</v>
       </c>
@@ -9553,7 +9552,7 @@
       <c r="L5" s="105">
         <v>699165.05217344186</v>
       </c>
-      <c r="N5" s="149"/>
+      <c r="N5" s="150"/>
       <c r="O5">
         <v>15</v>
       </c>
@@ -9614,7 +9613,7 @@
       <c r="L6" s="105">
         <v>0</v>
       </c>
-      <c r="N6" s="149"/>
+      <c r="N6" s="150"/>
       <c r="O6">
         <v>19</v>
       </c>
@@ -9675,7 +9674,7 @@
       <c r="L7" s="105">
         <v>265320.43464193383</v>
       </c>
-      <c r="N7" s="149"/>
+      <c r="N7" s="150"/>
       <c r="O7">
         <v>16</v>
       </c>
@@ -9736,7 +9735,7 @@
       <c r="L8" s="105">
         <v>454186.93616588484</v>
       </c>
-      <c r="N8" s="149"/>
+      <c r="N8" s="150"/>
       <c r="O8">
         <v>12</v>
       </c>
@@ -9797,7 +9796,7 @@
       <c r="L9" s="105">
         <v>801417.68719647545</v>
       </c>
-      <c r="N9" s="149"/>
+      <c r="N9" s="150"/>
       <c r="O9">
         <v>11</v>
       </c>
@@ -9854,7 +9853,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="110"/>
-      <c r="N10" s="149"/>
+      <c r="N10" s="150"/>
       <c r="O10">
         <v>8</v>
       </c>
@@ -9917,7 +9916,7 @@
       <c r="L11" s="103">
         <v>473999.33273359912</v>
       </c>
-      <c r="N11" s="149"/>
+      <c r="N11" s="150"/>
       <c r="O11">
         <v>52</v>
       </c>
@@ -9978,7 +9977,7 @@
       <c r="L12" s="105">
         <v>0</v>
       </c>
-      <c r="N12" s="149"/>
+      <c r="N12" s="150"/>
       <c r="O12">
         <v>53</v>
       </c>
@@ -10039,7 +10038,7 @@
       <c r="L13" s="105">
         <v>1774250.1300302623</v>
       </c>
-      <c r="N13" s="149"/>
+      <c r="N13" s="150"/>
       <c r="O13">
         <v>5</v>
       </c>
@@ -10100,7 +10099,7 @@
       <c r="L14" s="105">
         <v>688681.10694474855</v>
       </c>
-      <c r="N14" s="149"/>
+      <c r="N14" s="150"/>
       <c r="O14">
         <v>4</v>
       </c>
@@ -10161,7 +10160,7 @@
       <c r="L15" s="105">
         <v>542644.60453174426</v>
       </c>
-      <c r="N15" s="150"/>
+      <c r="N15" s="151"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="14"/>
@@ -10207,7 +10206,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L16" s="110"/>
-      <c r="N16" s="148" t="s">
+      <c r="N16" s="149" t="s">
         <v>38</v>
       </c>
       <c r="O16">
@@ -10272,7 +10271,7 @@
       <c r="L17" s="103">
         <v>0</v>
       </c>
-      <c r="N17" s="149"/>
+      <c r="N17" s="150"/>
       <c r="O17">
         <v>54</v>
       </c>
@@ -10333,7 +10332,7 @@
       <c r="L18" s="105">
         <v>0</v>
       </c>
-      <c r="N18" s="149"/>
+      <c r="N18" s="150"/>
       <c r="O18">
         <v>21</v>
       </c>
@@ -10394,7 +10393,7 @@
       <c r="L19" s="105">
         <v>0</v>
       </c>
-      <c r="N19" s="149"/>
+      <c r="N19" s="150"/>
       <c r="O19">
         <v>23</v>
       </c>
@@ -10455,7 +10454,7 @@
       <c r="L20" s="105">
         <v>532961.24250140926</v>
       </c>
-      <c r="N20" s="149"/>
+      <c r="N20" s="150"/>
       <c r="O20">
         <v>18</v>
       </c>
@@ -10516,7 +10515,7 @@
       <c r="L21" s="105">
         <v>243114.33850570052</v>
       </c>
-      <c r="N21" s="149"/>
+      <c r="N21" s="150"/>
       <c r="O21">
         <v>44</v>
       </c>
@@ -10577,7 +10576,7 @@
       <c r="L22" s="105">
         <v>399885.11500273226</v>
       </c>
-      <c r="N22" s="149"/>
+      <c r="N22" s="150"/>
       <c r="O22">
         <v>56</v>
       </c>
@@ -10638,7 +10637,7 @@
       <c r="L23" s="105">
         <v>0</v>
       </c>
-      <c r="N23" s="149"/>
+      <c r="N23" s="150"/>
       <c r="O23">
         <v>2</v>
       </c>
@@ -10699,7 +10698,7 @@
       <c r="L24" s="105">
         <v>532480.47978304385</v>
       </c>
-      <c r="N24" s="149"/>
+      <c r="N24" s="150"/>
       <c r="O24">
         <v>3</v>
       </c>
@@ -10760,7 +10759,7 @@
       <c r="L25" s="105">
         <v>855398.40214226511</v>
       </c>
-      <c r="N25" s="150"/>
+      <c r="N25" s="151"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="23"/>
       <c r="R25" s="14"/>
@@ -10806,7 +10805,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L26" s="110"/>
-      <c r="N26" s="148" t="s">
+      <c r="N26" s="149" t="s">
         <v>222</v>
       </c>
       <c r="O26">
@@ -10871,7 +10870,7 @@
       <c r="L27" s="103">
         <v>0</v>
       </c>
-      <c r="N27" s="149"/>
+      <c r="N27" s="150"/>
       <c r="O27">
         <v>36</v>
       </c>
@@ -10932,7 +10931,7 @@
       <c r="L28" s="105">
         <v>0</v>
       </c>
-      <c r="N28" s="149"/>
+      <c r="N28" s="150"/>
       <c r="O28">
         <v>9</v>
       </c>
@@ -10993,7 +10992,7 @@
       <c r="L29" s="105">
         <v>0</v>
       </c>
-      <c r="N29" s="149"/>
+      <c r="N29" s="150"/>
       <c r="O29">
         <v>40</v>
       </c>
@@ -11054,7 +11053,7 @@
       <c r="L30" s="105">
         <v>0</v>
       </c>
-      <c r="N30" s="149"/>
+      <c r="N30" s="150"/>
       <c r="O30">
         <v>27</v>
       </c>
@@ -11115,7 +11114,7 @@
       <c r="L31" s="105">
         <v>245173.74682820804</v>
       </c>
-      <c r="N31" s="149"/>
+      <c r="N31" s="150"/>
       <c r="O31">
         <v>10</v>
       </c>
@@ -11176,7 +11175,7 @@
       <c r="L32" s="105">
         <v>0</v>
       </c>
-      <c r="N32" s="149"/>
+      <c r="N32" s="150"/>
       <c r="O32">
         <v>28</v>
       </c>
@@ -11237,7 +11236,7 @@
       <c r="L33" s="105">
         <v>0</v>
       </c>
-      <c r="N33" s="149"/>
+      <c r="N33" s="150"/>
       <c r="O33">
         <v>33</v>
       </c>
@@ -11298,7 +11297,7 @@
       <c r="L34" s="105">
         <v>0</v>
       </c>
-      <c r="N34" s="149"/>
+      <c r="N34" s="150"/>
       <c r="O34">
         <v>37</v>
       </c>
@@ -11359,7 +11358,7 @@
       <c r="L35" s="105">
         <v>0</v>
       </c>
-      <c r="N35" s="149"/>
+      <c r="N35" s="150"/>
       <c r="O35">
         <v>24</v>
       </c>
@@ -11420,7 +11419,7 @@
       <c r="L36" s="105">
         <v>0</v>
       </c>
-      <c r="N36" s="149"/>
+      <c r="N36" s="150"/>
       <c r="O36">
         <v>7</v>
       </c>
@@ -11481,7 +11480,7 @@
       <c r="L37" s="105">
         <v>0</v>
       </c>
-      <c r="N37" s="149"/>
+      <c r="N37" s="150"/>
       <c r="O37">
         <v>57</v>
       </c>
@@ -11542,7 +11541,7 @@
       <c r="L38" s="105">
         <v>0</v>
       </c>
-      <c r="N38" s="149"/>
+      <c r="N38" s="150"/>
       <c r="O38">
         <v>1</v>
       </c>
@@ -11603,7 +11602,7 @@
       <c r="L39" s="105">
         <v>0</v>
       </c>
-      <c r="N39" s="150"/>
+      <c r="N39" s="151"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="23"/>
       <c r="R39" s="14"/>
@@ -13603,7 +13602,7 @@
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="2" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="2" bestFit="1" customWidth="1"/>
@@ -13653,7 +13652,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="143" t="s">
         <v>206</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -13667,12 +13666,11 @@
         <v>42285720.719740458</v>
       </c>
       <c r="E2" s="59">
-        <f>IFERROR(+VLOOKUP(C2,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>41610406.274805903</v>
       </c>
       <c r="F2" s="59">
         <f t="shared" ref="F2:F9" si="0">+D2-E2</f>
-        <v>42285720.719740458</v>
+        <v>675314.4449345544</v>
       </c>
       <c r="G2" s="60">
         <f t="shared" ref="G2:G47" si="1">+D2/C2</f>
@@ -13706,7 +13704,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="143"/>
+      <c r="A3" s="144"/>
       <c r="B3" s="36" t="s">
         <v>93</v>
       </c>
@@ -13718,12 +13716,11 @@
         <v>39460498.513925046</v>
       </c>
       <c r="E3" s="4">
-        <f>IFERROR(+VLOOKUP(C3,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>37706154.815905802</v>
       </c>
       <c r="F3" s="59">
         <f t="shared" si="0"/>
-        <v>39460498.513925046</v>
+        <v>1754343.6980192438</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" si="1"/>
@@ -13758,7 +13755,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="143"/>
+      <c r="A4" s="144"/>
       <c r="B4" s="36" t="s">
         <v>91</v>
       </c>
@@ -13770,12 +13767,11 @@
         <v>26520702.51038542</v>
       </c>
       <c r="E4" s="4">
-        <f>IFERROR(+VLOOKUP(C4,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>25390866.545600012</v>
       </c>
       <c r="F4" s="59">
         <f t="shared" si="0"/>
-        <v>26520702.51038542</v>
+        <v>1129835.9647854082</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="1"/>
@@ -13809,7 +13805,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="143"/>
+      <c r="A5" s="144"/>
       <c r="B5" s="36" t="s">
         <v>89</v>
       </c>
@@ -13821,12 +13817,11 @@
         <v>31676817.089343239</v>
       </c>
       <c r="E5" s="4">
-        <f>IFERROR(+VLOOKUP(C5,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>29335856.927223582</v>
       </c>
       <c r="F5" s="59">
         <f t="shared" si="0"/>
-        <v>31676817.089343239</v>
+        <v>2340960.1621196568</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="1"/>
@@ -13854,7 +13849,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="143"/>
+      <c r="A6" s="144"/>
       <c r="B6" s="36" t="s">
         <v>209</v>
       </c>
@@ -13866,12 +13861,11 @@
         <v>24141553.199037012</v>
       </c>
       <c r="E6" s="4">
-        <f>IFERROR(+VLOOKUP(C6,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>23409635.228719268</v>
       </c>
       <c r="F6" s="59">
         <f t="shared" si="0"/>
-        <v>24141553.199037012</v>
+        <v>731917.97031774372</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="1"/>
@@ -13899,7 +13893,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="143"/>
+      <c r="A7" s="144"/>
       <c r="B7" s="36" t="s">
         <v>271</v>
       </c>
@@ -13911,12 +13905,11 @@
         <v>17745499.922953639</v>
       </c>
       <c r="E7" s="4">
-        <f>IFERROR(+VLOOKUP(C7,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>16883619.323650431</v>
       </c>
       <c r="F7" s="59">
         <f t="shared" si="0"/>
-        <v>17745499.922953639</v>
+        <v>861880.59930320829</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
@@ -13944,7 +13937,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="143"/>
+      <c r="A8" s="144"/>
       <c r="B8" s="36" t="s">
         <v>84</v>
       </c>
@@ -13956,12 +13949,11 @@
         <v>35559935.88760341</v>
       </c>
       <c r="E8" s="4">
-        <f>IFERROR(+VLOOKUP(C8,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>34506733.881239109</v>
       </c>
       <c r="F8" s="59">
         <f t="shared" si="0"/>
-        <v>35559935.88760341</v>
+        <v>1053202.0063643008</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
@@ -13989,7 +13981,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="143"/>
+      <c r="A9" s="144"/>
       <c r="B9" s="36" t="s">
         <v>83</v>
       </c>
@@ -14001,12 +13993,11 @@
         <v>33858693.342466839</v>
       </c>
       <c r="E9" s="4">
-        <f>IFERROR(+VLOOKUP(C9,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>33030100.130732697</v>
       </c>
       <c r="F9" s="59">
         <f t="shared" si="0"/>
-        <v>33858693.342466839</v>
+        <v>828593.21173414215</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
@@ -14034,7 +14025,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="144"/>
+      <c r="A10" s="145"/>
       <c r="B10" s="3"/>
       <c r="C10" s="64">
         <v>242974591.73925051</v>
@@ -14044,12 +14035,11 @@
         <v>251249421.18545505</v>
       </c>
       <c r="E10" s="64">
-        <f>+SUM(E2:E9)</f>
-        <v>0</v>
+        <v>241873373.12787679</v>
       </c>
       <c r="F10" s="66">
         <f>+D10-E10</f>
-        <v>251249421.18545505</v>
+        <v>9376048.0575782657</v>
       </c>
       <c r="G10" s="65">
         <f t="shared" si="1"/>
@@ -14074,7 +14064,7 @@
       <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="142" t="s">
+      <c r="A11" s="143" t="s">
         <v>207</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -14088,12 +14078,11 @@
         <v>100110391.15793201</v>
       </c>
       <c r="E11" s="59">
-        <f>IFERROR(+VLOOKUP(C11,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>96700883.205506235</v>
       </c>
       <c r="F11" s="59">
         <f t="shared" ref="F11:F14" si="6">+D11-E11</f>
-        <v>100110391.15793201</v>
+        <v>3409507.9524257779</v>
       </c>
       <c r="G11" s="60">
         <f t="shared" si="1"/>
@@ -14121,7 +14110,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="143"/>
+      <c r="A12" s="144"/>
       <c r="B12" s="36" t="s">
         <v>90</v>
       </c>
@@ -14133,12 +14122,11 @@
         <v>102087212.84340489</v>
       </c>
       <c r="E12" s="4">
-        <f>IFERROR(+VLOOKUP(C12,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>102087212.84340489</v>
       </c>
       <c r="F12" s="59">
         <f t="shared" si="6"/>
-        <v>102087212.84340489</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
@@ -14172,7 +14160,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="143"/>
+      <c r="A13" s="144"/>
       <c r="B13" s="36" t="s">
         <v>272</v>
       </c>
@@ -14184,12 +14172,11 @@
         <v>34613285.663450733</v>
       </c>
       <c r="E13" s="4">
-        <f>IFERROR(+VLOOKUP(C13,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>34302310.373550735</v>
       </c>
       <c r="F13" s="59">
         <f t="shared" si="6"/>
-        <v>34613285.663450733</v>
+        <v>310975.28989999741</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
@@ -14218,7 +14205,7 @@
       <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="143"/>
+      <c r="A14" s="144"/>
       <c r="B14" s="36" t="s">
         <v>107</v>
       </c>
@@ -14230,12 +14217,11 @@
         <v>32905785.229168605</v>
       </c>
       <c r="E14" s="4">
-        <f>IFERROR(+VLOOKUP(C14,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>32498645.480668604</v>
       </c>
       <c r="F14" s="59">
         <f t="shared" si="6"/>
-        <v>32905785.229168605</v>
+        <v>407139.74850000069</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
@@ -14263,7 +14249,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="144"/>
+      <c r="A15" s="145"/>
       <c r="B15" s="3"/>
       <c r="C15" s="64">
         <v>341864881.75327951</v>
@@ -14273,12 +14259,11 @@
         <v>269716674.89395624</v>
       </c>
       <c r="E15" s="64">
-        <f>+SUM(E11:E14)</f>
-        <v>0</v>
+        <v>265589051.90313047</v>
       </c>
       <c r="F15" s="66">
         <f>+D15-E15</f>
-        <v>269716674.89395624</v>
+        <v>4127622.9908257723</v>
       </c>
       <c r="G15" s="65">
         <f t="shared" si="1"/>
@@ -14303,7 +14288,7 @@
       <c r="L15" s="67"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="146" t="s">
         <v>208</v>
       </c>
       <c r="B16" s="68" t="s">
@@ -14317,12 +14302,11 @@
         <v>13945934.946131114</v>
       </c>
       <c r="E16" s="59">
-        <f>IFERROR(+VLOOKUP(C16,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>13323959.077569095</v>
       </c>
       <c r="F16" s="59">
         <f t="shared" ref="F16:F46" si="7">+D16-E16</f>
-        <v>13945934.946131114</v>
+        <v>621975.8685620185</v>
       </c>
       <c r="G16" s="60">
         <f t="shared" si="1"/>
@@ -14350,7 +14334,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="146"/>
+      <c r="A17" s="147"/>
       <c r="B17" s="19" t="s">
         <v>82</v>
       </c>
@@ -14362,12 +14346,11 @@
         <v>24137576.900611538</v>
       </c>
       <c r="E17" s="4">
-        <f>IFERROR(+VLOOKUP(C17,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>23206009.330480266</v>
       </c>
       <c r="F17" s="59">
         <f t="shared" si="7"/>
-        <v>24137576.900611538</v>
+        <v>931567.57013127208</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
@@ -14395,7 +14378,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="146"/>
+      <c r="A18" s="147"/>
       <c r="B18" s="19" t="s">
         <v>92</v>
       </c>
@@ -14407,12 +14390,11 @@
         <v>21358590.673529468</v>
       </c>
       <c r="E18" s="4">
-        <f>IFERROR(+VLOOKUP(C18,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>20496296.761593435</v>
       </c>
       <c r="F18" s="59">
         <f t="shared" si="7"/>
-        <v>21358590.673529468</v>
+        <v>862293.91193603352</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
@@ -14440,7 +14422,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="146"/>
+      <c r="A19" s="147"/>
       <c r="B19" s="19" t="s">
         <v>95</v>
       </c>
@@ -14452,12 +14434,11 @@
         <v>35026761.331216544</v>
       </c>
       <c r="E19" s="4">
-        <f>IFERROR(+VLOOKUP(C19,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>34465432.612347864</v>
       </c>
       <c r="F19" s="59">
         <f t="shared" si="7"/>
-        <v>35026761.331216544</v>
+        <v>561328.7188686803</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
@@ -14485,7 +14466,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="146"/>
+      <c r="A20" s="147"/>
       <c r="B20" s="19" t="s">
         <v>97</v>
       </c>
@@ -14497,12 +14478,11 @@
         <v>15727434.484158095</v>
       </c>
       <c r="E20" s="4">
-        <f>IFERROR(+VLOOKUP(C20,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>15149311.124528823</v>
       </c>
       <c r="F20" s="59">
         <f t="shared" si="7"/>
-        <v>15727434.484158095</v>
+        <v>578123.35962927155</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
@@ -14530,7 +14510,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="146"/>
+      <c r="A21" s="147"/>
       <c r="B21" s="19" t="s">
         <v>219</v>
       </c>
@@ -14542,12 +14522,11 @@
         <v>26040173.304788072</v>
       </c>
       <c r="E21" s="4">
-        <f>IFERROR(+VLOOKUP(C21,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>25572672.63372704</v>
       </c>
       <c r="F21" s="59">
         <f t="shared" si="7"/>
-        <v>26040173.304788072</v>
+        <v>467500.67106103152</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
@@ -14575,7 +14554,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="146"/>
+      <c r="A22" s="147"/>
       <c r="B22" s="19" t="s">
         <v>160</v>
       </c>
@@ -14587,12 +14566,11 @@
         <v>22894552.211635783</v>
       </c>
       <c r="E22" s="4">
-        <f>IFERROR(+VLOOKUP(C22,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>22290249.207253531</v>
       </c>
       <c r="F22" s="59">
         <f t="shared" si="7"/>
-        <v>22894552.211635783</v>
+        <v>604303.00438225269</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
@@ -14620,7 +14598,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="146"/>
+      <c r="A23" s="147"/>
       <c r="B23" s="19" t="s">
         <v>220</v>
       </c>
@@ -14632,12 +14610,11 @@
         <v>37653118.237861037</v>
       </c>
       <c r="E23" s="4">
-        <f>IFERROR(+VLOOKUP(C23,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>37352638.429863513</v>
       </c>
       <c r="F23" s="59">
         <f t="shared" si="7"/>
-        <v>37653118.237861037</v>
+        <v>300479.80799752474</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
@@ -14665,7 +14642,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="147"/>
+      <c r="A24" s="148"/>
       <c r="B24" s="71"/>
       <c r="C24" s="66">
         <v>237630000</v>
@@ -14675,12 +14652,11 @@
         <v>196784142.08993167</v>
       </c>
       <c r="E24" s="66">
-        <f>+SUM(E16:E23)</f>
-        <v>0</v>
+        <v>191856569.17736357</v>
       </c>
       <c r="F24" s="66">
         <f>+D24-E24</f>
-        <v>196784142.08993167</v>
+        <v>4927572.9125680923</v>
       </c>
       <c r="G24" s="65">
         <f t="shared" si="1"/>
@@ -14705,7 +14681,7 @@
       <c r="L24" s="67"/>
     </row>
     <row r="25" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="142" t="s">
+      <c r="A25" s="143" t="s">
         <v>216</v>
       </c>
       <c r="B25" s="57" t="s">
@@ -14719,12 +14695,11 @@
         <v>60329801.152089536</v>
       </c>
       <c r="E25" s="59">
-        <f>IFERROR(+VLOOKUP(C25,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>57829766.086974263</v>
       </c>
       <c r="F25" s="59">
         <f t="shared" si="7"/>
-        <v>60329801.152089536</v>
+        <v>2500035.065115273</v>
       </c>
       <c r="G25" s="60">
         <f t="shared" si="1"/>
@@ -14752,7 +14727,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="143"/>
+      <c r="A26" s="144"/>
       <c r="B26" s="36" t="s">
         <v>213</v>
       </c>
@@ -14764,12 +14739,11 @@
         <v>12226089.901296066</v>
       </c>
       <c r="E26" s="4">
-        <f>IFERROR(+VLOOKUP(C26,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>11963691.606818626</v>
       </c>
       <c r="F26" s="59">
         <f t="shared" si="7"/>
-        <v>12226089.901296066</v>
+        <v>262398.29447744042</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
@@ -14797,7 +14771,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="143"/>
+      <c r="A27" s="144"/>
       <c r="B27" s="36" t="s">
         <v>86</v>
       </c>
@@ -14809,12 +14783,11 @@
         <v>14401052.837159272</v>
       </c>
       <c r="E27" s="4">
-        <f>IFERROR(+VLOOKUP(C27,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>13694761.317613492</v>
       </c>
       <c r="F27" s="59">
         <f t="shared" si="7"/>
-        <v>14401052.837159272</v>
+        <v>706291.51954578049</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
@@ -14843,7 +14816,7 @@
       <c r="M27" s="27"/>
     </row>
     <row r="28" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="143"/>
+      <c r="A28" s="144"/>
       <c r="B28" s="36" t="s">
         <v>212</v>
       </c>
@@ -14855,12 +14828,11 @@
         <v>19847876.635364786</v>
       </c>
       <c r="E28" s="4">
-        <f>IFERROR(+VLOOKUP(C28,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>19785141.165386483</v>
       </c>
       <c r="F28" s="59">
         <f t="shared" si="7"/>
-        <v>19847876.635364786</v>
+        <v>62735.469978302717</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
@@ -14889,7 +14861,7 @@
       <c r="M28" s="26"/>
     </row>
     <row r="29" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="143"/>
+      <c r="A29" s="144"/>
       <c r="B29" s="36" t="s">
         <v>98</v>
       </c>
@@ -14901,12 +14873,11 @@
         <v>22052328.865927253</v>
       </c>
       <c r="E29" s="4">
-        <f>IFERROR(+VLOOKUP(C29,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>21391786.042081032</v>
       </c>
       <c r="F29" s="59">
         <f t="shared" si="7"/>
-        <v>22052328.865927253</v>
+        <v>660542.82384622097</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
@@ -14935,7 +14906,7 @@
       <c r="M29" s="27"/>
     </row>
     <row r="30" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="143"/>
+      <c r="A30" s="144"/>
       <c r="B30" s="36" t="s">
         <v>210</v>
       </c>
@@ -14947,12 +14918,11 @@
         <v>14453628.378361048</v>
       </c>
       <c r="E30" s="4">
-        <f>IFERROR(+VLOOKUP(C30,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>14082645.129487799</v>
       </c>
       <c r="F30" s="59">
         <f t="shared" si="7"/>
-        <v>14453628.378361048</v>
+        <v>370983.2488732487</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
@@ -14981,7 +14951,7 @@
       <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="143"/>
+      <c r="A31" s="144"/>
       <c r="B31" s="36" t="s">
         <v>99</v>
       </c>
@@ -14993,12 +14963,11 @@
         <v>14944602.342241667</v>
       </c>
       <c r="E31" s="4">
-        <f>IFERROR(+VLOOKUP(C31,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>14568130.544950163</v>
       </c>
       <c r="F31" s="59">
         <f t="shared" si="7"/>
-        <v>14944602.342241667</v>
+        <v>376471.79729150422</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
@@ -15026,7 +14995,7 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="143"/>
+      <c r="A32" s="144"/>
       <c r="B32" s="36" t="s">
         <v>138</v>
       </c>
@@ -15038,12 +15007,11 @@
         <v>10133345.955324732</v>
       </c>
       <c r="E32" s="4">
-        <f>IFERROR(+VLOOKUP(C32,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>9735931.1299433764</v>
       </c>
       <c r="F32" s="59">
         <f t="shared" si="7"/>
-        <v>10133345.955324732</v>
+        <v>397414.82538135536</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
@@ -15071,7 +15039,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="143"/>
+      <c r="A33" s="144"/>
       <c r="B33" s="19" t="s">
         <v>274</v>
       </c>
@@ -15083,12 +15051,11 @@
         <v>5914861.5217189686</v>
       </c>
       <c r="E33" s="4">
-        <f>IFERROR(+VLOOKUP(C33,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>5709713.1251462931</v>
       </c>
       <c r="F33" s="59">
         <f t="shared" si="7"/>
-        <v>5914861.5217189686</v>
+        <v>205148.39657267556</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
@@ -15116,7 +15083,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="143"/>
+      <c r="A34" s="144"/>
       <c r="B34" s="36" t="s">
         <v>276</v>
       </c>
@@ -15128,12 +15095,11 @@
         <v>9560526.8965929467</v>
       </c>
       <c r="E34" s="4">
-        <f>IFERROR(+VLOOKUP(C34,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>9113051.1413762029</v>
       </c>
       <c r="F34" s="59">
         <f t="shared" si="7"/>
-        <v>9560526.8965929467</v>
+        <v>447475.7552167438</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
@@ -15161,7 +15127,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="143"/>
+      <c r="A35" s="144"/>
       <c r="B35" s="36" t="s">
         <v>110</v>
       </c>
@@ -15173,12 +15139,11 @@
         <v>78964296.522824496</v>
       </c>
       <c r="E35" s="4">
-        <f>IFERROR(+VLOOKUP(C35,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>78964296.522824496</v>
       </c>
       <c r="F35" s="59">
         <f t="shared" si="7"/>
-        <v>78964296.522824496</v>
+        <v>0</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
@@ -15206,7 +15171,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="143"/>
+      <c r="A36" s="144"/>
       <c r="B36" s="36" t="s">
         <v>214</v>
       </c>
@@ -15218,12 +15183,11 @@
         <v>14367535.716373395</v>
       </c>
       <c r="E36" s="4">
-        <f>IFERROR(+VLOOKUP(C36,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>14367535.716373395</v>
       </c>
       <c r="F36" s="59">
         <f t="shared" si="7"/>
-        <v>14367535.716373395</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
@@ -15251,7 +15215,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="143"/>
+      <c r="A37" s="144"/>
       <c r="B37" s="36" t="s">
         <v>80</v>
       </c>
@@ -15263,12 +15227,11 @@
         <v>21938268.016373243</v>
       </c>
       <c r="E37" s="4">
-        <f>IFERROR(+VLOOKUP(C37,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>21380620.494992524</v>
       </c>
       <c r="F37" s="59">
         <f t="shared" si="7"/>
-        <v>21938268.016373243</v>
+        <v>557647.5213807188</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
@@ -15296,7 +15259,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="144"/>
+      <c r="A38" s="145"/>
       <c r="B38" s="3"/>
       <c r="C38" s="74">
         <v>521754707.42240375</v>
@@ -15306,12 +15269,11 @@
         <v>299134214.74164742</v>
       </c>
       <c r="E38" s="66">
-        <f>+SUM(E25:E37)</f>
-        <v>0</v>
+        <v>292587070.0239681</v>
       </c>
       <c r="F38" s="66">
         <f>+D38-E38</f>
-        <v>299134214.74164742</v>
+        <v>6547144.7176793218</v>
       </c>
       <c r="G38" s="65">
         <f t="shared" si="1"/>
@@ -15336,7 +15298,7 @@
       <c r="L38" s="67"/>
     </row>
     <row r="39" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="142" t="s">
+      <c r="A39" s="143" t="s">
         <v>265</v>
       </c>
       <c r="B39" s="136" t="s">
@@ -15350,12 +15312,11 @@
         <v>24669197.621924087</v>
       </c>
       <c r="E39" s="4">
-        <f>IFERROR(+VLOOKUP(C39,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>23761816.928639762</v>
       </c>
       <c r="F39" s="59">
         <f t="shared" si="7"/>
-        <v>24669197.621924087</v>
+        <v>907380.6932843253</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
@@ -15383,7 +15344,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="143"/>
+      <c r="A40" s="144"/>
       <c r="B40" s="136" t="s">
         <v>145</v>
       </c>
@@ -15395,12 +15356,11 @@
         <v>14499068.612910941</v>
       </c>
       <c r="E40" s="4">
-        <f>IFERROR(+VLOOKUP(C40,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>12804899.463654276</v>
       </c>
       <c r="F40" s="59">
         <f t="shared" si="7"/>
-        <v>14499068.612910941</v>
+        <v>1694169.1492566653</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="1"/>
@@ -15428,7 +15388,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="143"/>
+      <c r="A41" s="144"/>
       <c r="B41" s="136" t="s">
         <v>106</v>
       </c>
@@ -15440,12 +15400,11 @@
         <v>19388227.995180633</v>
       </c>
       <c r="E41" s="4">
-        <f>IFERROR(+VLOOKUP(C41,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>19388227.995180633</v>
       </c>
       <c r="F41" s="59">
         <f t="shared" si="7"/>
-        <v>19388227.995180633</v>
+        <v>0</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="1"/>
@@ -15473,7 +15432,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="143"/>
+      <c r="A42" s="144"/>
       <c r="B42" s="137" t="s">
         <v>139</v>
       </c>
@@ -15485,12 +15444,11 @@
         <v>59139346.928738102</v>
       </c>
       <c r="E42" s="4">
-        <f>IFERROR(+VLOOKUP(C42,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>59139346.928738102</v>
       </c>
       <c r="F42" s="59">
         <f t="shared" si="7"/>
-        <v>59139346.928738102</v>
+        <v>0</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="1"/>
@@ -15518,7 +15476,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="143"/>
+      <c r="A43" s="144"/>
       <c r="B43" s="138" t="s">
         <v>266</v>
       </c>
@@ -15530,12 +15488,11 @@
         <v>55057645.412610985</v>
       </c>
       <c r="E43" s="4">
-        <f>IFERROR(+VLOOKUP(C43,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>55057645.412610985</v>
       </c>
       <c r="F43" s="59">
         <f t="shared" si="7"/>
-        <v>55057645.412610985</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="1"/>
@@ -15563,7 +15520,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="143"/>
+      <c r="A44" s="144"/>
       <c r="B44" s="138" t="s">
         <v>267</v>
       </c>
@@ -15575,12 +15532,11 @@
         <v>81530925.666284323</v>
       </c>
       <c r="E44" s="4">
-        <f>IFERROR(+VLOOKUP(C44,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>81717971.005489424</v>
       </c>
       <c r="F44" s="59">
         <f t="shared" si="7"/>
-        <v>81530925.666284323</v>
+        <v>-187045.33920510113</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="1"/>
@@ -15608,7 +15564,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="143"/>
+      <c r="A45" s="144"/>
       <c r="B45" s="138" t="s">
         <v>275</v>
       </c>
@@ -15620,12 +15576,11 @@
         <v>7202966.5073920414</v>
       </c>
       <c r="E45" s="4">
-        <f>IFERROR(+VLOOKUP(C45,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>7202966.5073920414</v>
       </c>
       <c r="F45" s="59">
         <f t="shared" si="7"/>
-        <v>7202966.5073920414</v>
+        <v>0</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="1"/>
@@ -15653,7 +15608,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="143"/>
+      <c r="A46" s="144"/>
       <c r="B46" s="138" t="s">
         <v>268</v>
       </c>
@@ -15665,12 +15620,11 @@
         <v>35321218.174947955</v>
       </c>
       <c r="E46" s="4">
-        <f>IFERROR(+VLOOKUP(C46,COMISIONES!B:F,5,FALSE),"0")*1</f>
-        <v>0</v>
+        <v>24185979.343219414</v>
       </c>
       <c r="F46" s="59">
         <f t="shared" si="7"/>
-        <v>35321218.174947955</v>
+        <v>11135238.83172854</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="1"/>
@@ -15698,7 +15652,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="144"/>
+      <c r="A47" s="145"/>
       <c r="B47" s="135"/>
       <c r="C47" s="66">
         <v>455695855.27356702</v>
@@ -15708,12 +15662,11 @@
         <v>296808596.91998911</v>
       </c>
       <c r="E47" s="66">
-        <f>SUM(E39:E46)</f>
-        <v>0</v>
+        <v>283258853.58492464</v>
       </c>
       <c r="F47" s="66">
         <f>+SUM(F39:F46)</f>
-        <v>296808596.91998911</v>
+        <v>13549743.33506443</v>
       </c>
       <c r="G47" s="65">
         <f t="shared" si="1"/>
@@ -15750,12 +15703,11 @@
         <v>1313693049.8309796</v>
       </c>
       <c r="E48" s="77">
-        <f>+E38+E24+E10+E15+E47</f>
-        <v>0</v>
+        <v>1275164917.8172636</v>
       </c>
       <c r="F48" s="77">
         <f>+D48-E48</f>
-        <v>1313693049.8309796</v>
+        <v>38528132.013715982</v>
       </c>
       <c r="G48" s="78">
         <f>+D48/C48</f>
@@ -16588,7 +16540,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="149" t="s">
         <v>38</v>
       </c>
       <c r="B15">
@@ -16629,7 +16581,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="149"/>
+      <c r="A16" s="150"/>
       <c r="B16">
         <v>54</v>
       </c>
@@ -16668,7 +16620,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="149"/>
+      <c r="A17" s="150"/>
       <c r="B17">
         <v>21</v>
       </c>
@@ -16707,7 +16659,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="149"/>
+      <c r="A18" s="150"/>
       <c r="B18">
         <v>23</v>
       </c>
@@ -16746,7 +16698,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="149"/>
+      <c r="A19" s="150"/>
       <c r="B19">
         <v>18</v>
       </c>
@@ -16785,7 +16737,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="149"/>
+      <c r="A20" s="150"/>
       <c r="B20">
         <v>44</v>
       </c>
@@ -16824,7 +16776,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="149"/>
+      <c r="A21" s="150"/>
       <c r="B21">
         <v>2</v>
       </c>
@@ -16863,7 +16815,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="149"/>
+      <c r="A22" s="150"/>
       <c r="B22">
         <v>3</v>
       </c>
@@ -16902,7 +16854,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="150"/>
+      <c r="A23" s="151"/>
       <c r="C23" s="9"/>
       <c r="D23" s="23"/>
       <c r="E23" s="14"/>
@@ -16921,7 +16873,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="148" t="s">
+      <c r="A24" s="149" t="s">
         <v>215</v>
       </c>
       <c r="B24">
@@ -16962,7 +16914,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="149"/>
+      <c r="A25" s="150"/>
       <c r="B25">
         <v>36</v>
       </c>
@@ -17001,7 +16953,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="149"/>
+      <c r="A26" s="150"/>
       <c r="B26">
         <v>9</v>
       </c>
@@ -17040,7 +16992,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="149"/>
+      <c r="A27" s="150"/>
       <c r="B27">
         <v>40</v>
       </c>
@@ -17079,7 +17031,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="149"/>
+      <c r="A28" s="150"/>
       <c r="B28">
         <v>27</v>
       </c>
@@ -17118,7 +17070,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="149"/>
+      <c r="A29" s="150"/>
       <c r="B29">
         <v>10</v>
       </c>
@@ -17157,7 +17109,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="149"/>
+      <c r="A30" s="150"/>
       <c r="B30">
         <v>28</v>
       </c>
@@ -17196,7 +17148,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="149"/>
+      <c r="A31" s="150"/>
       <c r="B31">
         <v>33</v>
       </c>
@@ -17235,7 +17187,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="149"/>
+      <c r="A32" s="150"/>
       <c r="B32">
         <v>37</v>
       </c>
@@ -17274,7 +17226,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="149"/>
+      <c r="A33" s="150"/>
       <c r="B33">
         <v>24</v>
       </c>
@@ -17313,7 +17265,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="149"/>
+      <c r="A34" s="150"/>
       <c r="B34">
         <v>7</v>
       </c>
@@ -17349,7 +17301,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="149"/>
+      <c r="A35" s="150"/>
       <c r="B35">
         <v>57</v>
       </c>
@@ -17385,7 +17337,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="149"/>
+      <c r="A36" s="150"/>
       <c r="B36">
         <v>1</v>
       </c>
@@ -17424,7 +17376,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="150"/>
+      <c r="A37" s="151"/>
       <c r="C37" s="9"/>
       <c r="D37" s="23"/>
       <c r="E37" s="14"/>
@@ -17443,7 +17395,7 @@
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="148" t="s">
+      <c r="A38" s="149" t="s">
         <v>269</v>
       </c>
       <c r="B38">
@@ -17478,7 +17430,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="149"/>
+      <c r="A39" s="150"/>
       <c r="B39">
         <v>59</v>
       </c>
@@ -17511,7 +17463,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="149"/>
+      <c r="A40" s="150"/>
       <c r="B40">
         <v>49</v>
       </c>
@@ -17544,7 +17496,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="149"/>
+      <c r="A41" s="150"/>
       <c r="B41">
         <v>56</v>
       </c>
@@ -17577,7 +17529,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="149"/>
+      <c r="A42" s="150"/>
       <c r="B42">
         <v>26</v>
       </c>
@@ -17610,7 +17562,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="149"/>
+      <c r="A43" s="150"/>
       <c r="B43">
         <v>25</v>
       </c>
@@ -17643,7 +17595,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="149"/>
+      <c r="A44" s="150"/>
       <c r="B44">
         <v>60</v>
       </c>
@@ -17676,7 +17628,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="149"/>
+      <c r="A45" s="150"/>
       <c r="B45">
         <v>43</v>
       </c>
